--- a/data/MK_INV_DATA_20260609.xlsx
+++ b/data/MK_INV_DATA_20260609.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1515.46</v>
+        <v>1512.61</v>
       </c>
       <c r="F29" t="n">
         <v>1526.82</v>
@@ -1479,11 +1479,11 @@
         <v>1533.02</v>
       </c>
       <c r="H29" t="n">
-        <v>1513.68</v>
+        <v>1508.98</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>-0.0251</v>
+        <v>-0.0269</v>
       </c>
     </row>
     <row r="30">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223.58</v>
+        <v>223.51</v>
       </c>
       <c r="F30" t="n">
         <v>225.83</v>
@@ -1515,7 +1515,7 @@
         <v>225.99</v>
       </c>
       <c r="H30" t="n">
-        <v>223.51</v>
+        <v>223.07</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9.433</v>
+        <v>9.426</v>
       </c>
       <c r="F58" t="n">
         <v>9.512</v>
@@ -2519,11 +2519,11 @@
         <v>9.547000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>9.433</v>
+        <v>9.407999999999999</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>-0.0268</v>
+        <v>-0.0276</v>
       </c>
     </row>
     <row r="59">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>90.15000000000001</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="F112" t="n">
         <v>91.28</v>
@@ -4459,11 +4459,11 @@
         <v>91.55</v>
       </c>
       <c r="H112" t="n">
-        <v>89.84999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>-0.0126</v>
+        <v>-0.0174</v>
       </c>
     </row>
     <row r="113">
@@ -5524,24 +5524,24 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4355.6</v>
+        <v>4367.3</v>
       </c>
       <c r="F139" t="n">
         <v>4354.7</v>
       </c>
       <c r="G139" t="n">
-        <v>4366.5</v>
+        <v>4375.7</v>
       </c>
       <c r="H139" t="n">
         <v>4336</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>17.62K</t>
+          <t>21.53K</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>0.0045</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="140">
@@ -9176,24 +9176,24 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>8047.71</v>
+        <v>8064.01</v>
       </c>
       <c r="F238" t="n">
         <v>7697.76</v>
       </c>
       <c r="G238" t="n">
-        <v>8086.47</v>
+        <v>8119.09</v>
       </c>
       <c r="H238" t="n">
         <v>7598.87</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>357.15K</t>
+          <t>415.32K</t>
         </is>
       </c>
       <c r="J238" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="239">
@@ -10134,24 +10134,24 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1283.04</v>
+        <v>1287.25</v>
       </c>
       <c r="F262" t="n">
         <v>1221.75</v>
       </c>
       <c r="G262" t="n">
-        <v>1290.59</v>
+        <v>1297.79</v>
       </c>
       <c r="H262" t="n">
         <v>1206.94</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>157.10K</t>
+          <t>185.58K</t>
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.0813</v>
+        <v>0.0849</v>
       </c>
     </row>
     <row r="263">
@@ -11092,24 +11092,24 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>979.63</v>
+        <v>965.79</v>
       </c>
       <c r="F286" t="n">
         <v>937.6900000000001</v>
       </c>
       <c r="G286" t="n">
-        <v>979.63</v>
+        <v>981.24</v>
       </c>
       <c r="H286" t="n">
         <v>937.04</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>515.23K</t>
+          <t>591.09K</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="287">

--- a/data/MK_INV_DATA_20260609.xlsx
+++ b/data/MK_INV_DATA_20260609.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1512.61</v>
+        <v>1514.28</v>
       </c>
       <c r="F29" t="n">
         <v>1526.82</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>-0.0269</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="30">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223.51</v>
+        <v>223.67</v>
       </c>
       <c r="F30" t="n">
         <v>225.83</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9.426</v>
+        <v>9.433999999999999</v>
       </c>
       <c r="F58" t="n">
         <v>9.512</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>-0.0276</v>
+        <v>-0.0267</v>
       </c>
     </row>
     <row r="59">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>89.70999999999999</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F112" t="n">
         <v>91.28</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>-0.0174</v>
+        <v>-0.0143</v>
       </c>
     </row>
     <row r="113">
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4367.3</v>
+        <v>4359.9</v>
       </c>
       <c r="F139" t="n">
         <v>4354.7</v>
@@ -5537,11 +5537,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>21.53K</t>
+          <t>22.26K</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>0.0072</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="140">
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>8064.01</v>
+        <v>8107.88</v>
       </c>
       <c r="F238" t="n">
         <v>7697.76</v>
@@ -9189,11 +9189,11 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>415.32K</t>
+          <t>429.37K</t>
         </is>
       </c>
       <c r="J238" t="n">
-        <v>0.0774</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="239">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1287.25</v>
+        <v>1294.88</v>
       </c>
       <c r="F262" t="n">
         <v>1221.75</v>
@@ -10147,11 +10147,11 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>185.58K</t>
+          <t>191.64K</t>
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.0849</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="263">
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>965.79</v>
+        <v>968.37</v>
       </c>
       <c r="F286" t="n">
         <v>937.6900000000001</v>
@@ -11105,11 +11105,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>591.09K</t>
+          <t>608.17K</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>0.0597</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="287">

--- a/data/MK_INV_DATA_20260609.xlsx
+++ b/data/MK_INV_DATA_20260609.xlsx
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1514.28</v>
+        <v>1516.52</v>
       </c>
       <c r="F29" t="n">
         <v>1526.82</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>-0.0259</v>
+        <v>-0.0244</v>
       </c>
     </row>
     <row r="30">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>223.67</v>
+        <v>224.01</v>
       </c>
       <c r="F30" t="n">
         <v>225.83</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9.433999999999999</v>
+        <v>9.449</v>
       </c>
       <c r="F58" t="n">
         <v>9.512</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>-0.0267</v>
+        <v>-0.0252</v>
       </c>
     </row>
     <row r="59">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>89.98999999999999</v>
+        <v>89.92</v>
       </c>
       <c r="F112" t="n">
         <v>91.28</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>-0.0143</v>
+        <v>-0.0151</v>
       </c>
     </row>
     <row r="113">
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4359.9</v>
+        <v>4361.3</v>
       </c>
       <c r="F139" t="n">
         <v>4354.7</v>
@@ -5537,11 +5537,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>22.26K</t>
+          <t>23.11K</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="140">
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>8107.88</v>
+        <v>8096.93</v>
       </c>
       <c r="F238" t="n">
         <v>7697.76</v>
@@ -9189,11 +9189,11 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>429.37K</t>
+          <t>442.43K</t>
         </is>
       </c>
       <c r="J238" t="n">
-        <v>0.0833</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="239">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1294.88</v>
+        <v>1293.4</v>
       </c>
       <c r="F262" t="n">
         <v>1221.75</v>
@@ -10147,11 +10147,11 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>191.64K</t>
+          <t>201.41K</t>
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="263">
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>968.37</v>
+        <v>967.8099999999999</v>
       </c>
       <c r="F286" t="n">
         <v>937.6900000000001</v>
@@ -11105,11 +11105,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>608.17K</t>
+          <t>615.19K</t>
         </is>
       </c>
       <c r="J286" t="n">
-        <v>0.0625</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="287">
